--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -438,7 +438,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="4" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -585,35 +585,6 @@
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="9">
-      <c r="A9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>"Label en el celular"</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>En tus notas escribiste "Label en el celular" pero no aparece en ningún audio. Marcá UNA opción:
-(a) imprimir desde el teléfono a una etiquetadora Bluetooth
-(b) que el operario vea la etiqueta en pantalla, sin imprimir
-(c) escanear la etiqueta con el teléfono en vez del pistolete
-(d) que el cliente la vea desde su celular</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Apareció justo cuando comentabas que se te dañó la impresora, así que sospechamos que va por ahí. Si es (d), sale de este bloque de trabajo y se cotiza aparte porque es portal del cliente, no operación de Miami.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -438,7 +438,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="4" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -621,20 +621,45 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>Código del supervisor</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Para armar lo del código: ¿es un PIN corto aparte, distinto de la contraseña con la que el supervisor entra al sistema? ¿Destraba solo el precio o también descuentos y quitar líneas? ¿Autoriza toda la pre-factura o línea por línea?</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Nos aclaraste que "tarifa editable con autorización de supervisor o jefe" es una función del sistema, no de tu proceso: el precio sale bloqueado en la pre-factura y el supervisor lo destraba con su código. Nuestra apuesta: PIN corto aparte, porque es lo práctico con el cajero sentado enfrente.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="90" r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>Etiqueta — qué cabe</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>La etiqueta de ETIQUETAR mide 2.25 x 1.25 pulgadas (Dymo). A ese tamaño NO caben los 11 campos legibles con el código de barras encima. ¿Cuáles son los 4 o 5 imprescindibles, los que el operario tiene que leer de lejos en la estantería?</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Nuestra apuesta: (1) código de barras, (2) número de recepción, (3) código + nombre del cliente, (4) sucursal donde retira, (5) n/N de paquetes. Los 11 campos están listados en la hoja 3.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -621,17 +621,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Código del supervisor</t>
+          <t>Descuento como campo propio</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Para armar lo del código: ¿es un PIN corto aparte, distinto de la contraseña con la que el supervisor entra al sistema? ¿Destraba solo el precio o también descuentos y quitar líneas? ¿Autoriza toda la pre-factura o línea por línea?</t>
+          <t>Para el código del supervisor ya nos diste todo (PIN de 4 dígitos, por línea, destraba precio/descuento/quitar líneas/peso). Solo queda esto: hoy el descuento NO existe como dato — se hace bajándole el precio a la línea. ¿Lo convertimos en un campo propio, para que la factura diga que hubo descuento y de cuánto?</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Nos aclaraste que "tarifa editable con autorización de supervisor o jefe" es una función del sistema, no de tu proceso: el precio sale bloqueado en la pre-factura y el supervisor lo destraba con su código. Nuestra apuesta: PIN corto aparte, porque es lo práctico con el cajero sentado enfrente.</t>
+          <t>Como está hoy, un descuento es invisible: la factura sale con un precio más bajo y nada dice que fue un descuento, ni de cuánto, ni quién lo dio. Si el PIN va a autorizar descuentos, conviene que el descuento se vea.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -621,17 +621,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Descuento como campo propio</t>
+          <t>PINs de los supervisores</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Para el código del supervisor ya nos diste todo (PIN de 4 dígitos, por línea, destraba precio/descuento/quitar líneas/peso). Solo queda esto: hoy el descuento NO existe como dato — se hace bajándole el precio a la línea. ¿Lo convertimos en un campo propio, para que la factura diga que hubo descuento y de cuánto?</t>
+          <t>El código del supervisor ya está funcionando. Falta que nos digas a quiénes les asignamos PIN — cualquiera de estos cuatro roles puede tener uno: Administrador, Supervisor Caja, Supervisor Pre-Factura y Supervisor de Servicio al Cliente.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Como está hoy, un descuento es invisible: la factura sale con un precio más bajo y nada dice que fue un descuento, ni de cuánto, ni quién lo dio. Si el PIN va a autorizar descuentos, conviene que el descuento se vea.</t>
+          <t>Un administrador se los asigna desde la pantalla de usuarios y después cada supervisor lo cambia por uno que solo él sepa. Mientras no lo cambie, el administrador conoce el PIN con el que ese supervisor autoriza — la pantalla de usuarios marca a quiénes les falta cambiarlo.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -3988,7 +3988,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Estos son los 11 campos que anotaste en la etiqueta que mandaste. Marcá con una X los que SÍ o SÍ tienen que ir, sabiendo que a ese tamaño no caben todos.</t>
+          <t>Los 11 campos que anotaste. Nos dijiste que el tamaño de la etiqueta no cambia y que "allí es letra pequeña unas y otras grandes", así que van los 11 con jerarquía de tamaño. Esta hoja queda de referencia: si algo sale mal impreso, marcalo en la última columna.</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>¿Imprescindible? (X)</t>
+          <t>¿Sale bien impreso?</t>
         </is>
       </c>
     </row>

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -6,6 +6,7 @@
     <sheet sheetId="1" name="1. Preguntas" r:id="rId1"/>
     <sheet sheetId="2" name="2. Tarifas cargadas" r:id="rId2"/>
     <sheet sheetId="3" name="3. Etiqueta" r:id="rId3"/>
+    <sheet sheetId="4" name="4. Cargos" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -506,7 +507,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". Los 16 cargos que no son flete (recolecta, retenido, entrega nacional, manejo…) NO se cargaron todavía: son otro módulo del sistema y varios ya existen con otros valores, así que los vamos a reconciliar aparte.</t>
+          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". De los 16 cargos que no son flete cargamos 5 (entrega nacional, compra online, manejo y gastos, flete internacional UPS y retornado en Miami); los otros 10 estan en la hoja 4 esperando que nos digas la moneda.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -4390,4 +4391,499 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <cols>
+    <col width="30" min="1" max="1" bestFit="1" customWidth="1"/>
+    <col width="20" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="20" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="62" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="20" min="5" max="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Cargos que no son flete — nos falta la moneda</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>En tu hoja pusiste la leyenda "precios en $" y "precios en lempiras", pero las celdas de precio quedaron sin colorear. Viendo solo el numero no hay como saber si un 5 son cinco dolares o cinco lempiras, y preferimos preguntarte antes que adivinar: son montos que se le cobran al cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>YA CARGADOS — estos los dejaste claros en la misma hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Como lo supimos</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Entrega nacional</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>86.96</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>LPS</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>El titulo dice L100, y 86.96 mas ISV da L.100.00 exactos</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Compra online</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Tu nota: "ponerlo $1 mas isv"</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Manejo y gastos de destino</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LPS</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Tu nota: "ponerlo lps1 mas isv"</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Flete internacional UPS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>El titulo de la fila dice "$1"</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Retornado en Miami</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Tu nota: "todo en $"</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="11"/>
+    <row customHeight="1" ht="34" r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>NOS FALTAN ESTOS — escribi la moneda en la columna amarilla</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Valor en tu hoja</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Que anotaste</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Nuestra duda</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>MONEDA ($ o LPS)</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Cambio de servicio</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>5 (titulo dice L100)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>pasarlo a dolares</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>OJO: hoy el sistema lo tiene en $15 y se cobra SOLO, en nota de debito, cada vez que se factura un paquete al que le cambiaron el servicio. Mientras no confirmes sigue cobrando $15.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Retenido Miami</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>pasarlo a dolares</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>El 5 ya es dolares, o todavia hay que convertirlo?</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Servicio de entrada y salida</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>10 (minimo 5)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>pasarlo a dolares</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Misma duda</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Recolecta Miami</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>35 (minimo 35)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Vos mismo pediste que la recolecta fuera por ZONA y no $35 fijos, y asi esta hecho. Dejamos la tabla por zona o la cambiamos a 35 plano?</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Ajuste</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>En que moneda, y que ajusta exactamente?</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Entrega local</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1 (titulo dice L1)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>El titulo dice L1 pero no hay nota que lo confirme</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Consolidando en Miami</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>En que moneda?</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Flete Mexico</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>5 (minimo 6)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>En que moneda?</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Flete</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Este es el flete del paquete, que ya sale de la tabla de tarifas. Lo dejamos fuera; confirmanos si te parece.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="34" r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Producto ejemplo (y en dolares)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>4 y 10</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Los tomamos como datos de prueba. Confirmanos que no van.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -439,228 +439,426 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="4" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="18" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="52" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="58" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="34" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="10" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="20" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="50" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="56" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="32" min="6" max="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Preguntas para Yusef — 2026-08-05</t>
+          <t>Preguntas para Yusef — 06 de Agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Llená solo la columna amarilla. Lo demás es contexto para que no tengas que acordarte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row customHeight="1" ht="90" r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Llená solo la columna amarilla. Lo demás es contexto para que no tengas que acordarte de nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Están en orden de urgencia: las primeras son las que hoy hacen que el sistema cobre distinto de lo que vos querés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row customHeight="1" ht="78" r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Urgencia</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Pregunta</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Lo que sabemos hoy</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>TU RESPUESTA</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="90" r="5">
-      <c r="A5" s="6" t="n">
+    <row customHeight="1" ht="78" r="6">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Precios cargados</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Ya cargamos tu tabla PROPUESTA al sistema. En la hoja 2 está TODO lo que quedó cargado, exactamente como lo va a cobrar el sistema. ¿Está bien?</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". De los 16 cargos que no son flete cargamos 5 (entrega nacional, compra online, manejo y gastos, flete internacional UPS y retornado en Miami); los otros 10 estan en la hoja 4 esperando que nos digas la moneda.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="6">
-      <c r="A6" s="6" t="n">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Cambio de servicio</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>En tu hoja el cambio de servicio dice 5 y el titulo dice L100, con la nota "pasarlo a dolares". En el sistema esta cargado en $15. ¿Cual queda?</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Este cargo se genera SOLO, en una nota de debito, cada vez que se factura un paquete al que le cambiaron el servicio. Mientras no nos digas, sigue cobrando los $15 — que es el triple de los 5 de tu hoja.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="7">
+      <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Mínimo CEM y CKM en libras</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>¿Hace falta todavía un mínimo en LIBRAS para CEM y CKM, o con el mínimo en dinero de la tabla ya está?</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Tu tabla trae el mínimo en dinero (L.200 con ISV) pero no el de libras. En la práctica el escalonado ya cubre el paquete chico: un CEM de 2 libras paga 4.50/lb = $9. Documentado en abril: CEM = 8 libras, CKM = 20 libras. En el audio dijiste 3 o 4 libras.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="7">
-      <c r="A7" s="6" t="n">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Moneda de 10 cargos</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Necesitamos la moneda de 10 cargos de tu hoja. Estan en la HOJA 4 con la duda de cada uno y una columna para que escribas $ o LPS.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>En tu hoja pusiste la leyenda "precios en $" y "precios en lempiras" pero las celdas de precio quedaron sin colorear, asi que un 5 no dice si son 5 dolares o 5 lempiras. Ya cargamos los 5 que si dejaste claros con una nota escrita.</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="8">
+      <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Recolecta: ¿zona o plano?</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Vos pediste que la recolecta se cobrara POR ZONA en vez de $35 fijos, y asi esta hecho. Pero tu hoja nueva dice 35 plano. ¿Cual mandamos?</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Hoy el sistema tiene una tabla de tarifas de recolecta por zona/distancia, que es lo que pediste en su momento. Si mandamos el 35 plano, esa tabla deja de usarse.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="9">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Revisar los precios cargados</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>En la HOJA 2 esta TODO lo que quedo cargado de tu tabla, leido directo del sistema. Es literalmente lo que va a cobrar. ¿Esta bien?</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". Si algo esta mal, escribilo en la ultima columna de esa hoja.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="10">
+      <c r="A10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Las categorías no bajan de escalón</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Un cliente "Clientes Amigos" con 200 libras de CER paga $4.20 la libra ($840) mientras el publico paga $3.50 ($700). ¿Es asi, o las categorias tambien deberian bajar de escalon?</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Tu tabla da un solo precio por categoria (columna NORMAL) y los tarifarios escalonados los declaraste solo para el Precio Normal. Lo cargamos literal a como lo mandaste, pero el resultado es que un amigo paga mas que un cliente de mostrador en paquetes grandes.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="11">
+      <c r="A11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>CKM cae en dos reglas</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Para CKM, ¿cuál mínimo manda: los L.200, el de libras, o el que resulte MAYOR de los dos?</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>En el audio dijiste "los servicios serie CK son 200 lempiras ya con ISV" (aplica a CKA y CKM) y también "el marítimo lo tenemos estipulado en cantidad de libras" (aplica a CEM y CKM). CKM es las dos cosas. En tu tabla le pusiste L.173.91, así que cargamos ese — confirmalo.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="8">
-      <c r="A8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Categorías que no vinieron</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>En el sistema hay 8 clientes en las categorías "Regular" y "VIP", que no aparecen en tu tabla. ¿A cuál de las nuevas los pasamos, o los dejamos como están?</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Las categorías de tu tabla son: Clientes Amigos, doTERRA/Farmasi, Familia, Mayoristas, Personal de CEC, Shein, Revendedores y Sin Cobro Mínimo. Familia y Revendedores vinieron en cero, así que por ahora sus clientes pagan precio de lista. Mayoristas solo trae el precio de CKM.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="9">
-      <c r="A9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Descuento y escalones</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Un cliente "Clientes Amigos" con 200 libras de CER paga $4.20 la libra ($840) mientras el público paga $3.50 ($700), porque el escalonado solo lo pusiste en el precio de lista. ¿Es así o las categorías también bajan de escalón?</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Tu tabla da un solo precio por categoría (columna NORMAL) y los tarifarios escalonados están declarados solo para el Precio Normal. Lo cargamos literal a como lo mandaste.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="10">
-      <c r="A10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Para CKM, ¿cual minimo manda: los L.200, el de libras, o el que resulte MAYOR de los dos?</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>En el audio dijiste "los servicios serie CK son 200 lempiras ya con ISV" (aplica a CKA y CKM) y tambien "el maritimo lo tenemos estipulado en cantidad de libras" (aplica a CEM y CKM). CKM es las dos cosas. En tu tabla le pusiste L.173.91, asi que cargamos ese.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="12">
+      <c r="A12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Mínimo en libras de CEM y CKM</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>¿Hace falta todavia un minimo en LIBRAS para CEM y CKM, o con el minimo en dinero de tu tabla ya esta?</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Tu tabla trae el minimo en dinero (L.200 con ISV) pero no el de libras. En la practica el escalonado ya cubre el paquete chico: un CEM de 2 libras paga $4.50 la libra. Documentado en abril: CEM = 8 libras, CKM = 20 libras. En el audio dijiste 3 o 4 libras.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="13">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Regular y VIP</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Hay 8 clientes en las categorias "Regular" y "VIP", que no aparecen en tu tabla. ¿A cual de las nuevas los pasamos, o los dejamos como estan?</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Por ahora se quedaron con los precios viejos, que son mas bajos que los de lista. Las categorias de tu tabla son: Clientes Amigos, doTERRA/Farmasi, Familia, Mayoristas, Personal de CEC, Shein, Revendedores y Sin Cobro Minimo.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="14">
+      <c r="A14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Mayoristas incompleto</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>De MAYORISTAS solo vino el precio de CKM ($1.50). Los otros cuatro servicios vinieron en cero. ¿Que cobran los mayoristas en CER, CKA, EXPRESS y CEM?</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Mientras tanto esos cuatro siguen con los valores viejos del sistema, que no salieron de tu tabla. FAMILIA y REVENDEDORES vinieron todos en cero, asi que sus clientes pagan precio de lista.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="15">
+      <c r="A15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>PINs de los supervisores</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>El código del supervisor ya está funcionando. Falta que nos digas a quiénes les asignamos PIN — cualquiera de estos cuatro roles puede tener uno: Administrador, Supervisor Caja, Supervisor Pre-Factura y Supervisor de Servicio al Cliente.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Un administrador se los asigna desde la pantalla de usuarios y después cada supervisor lo cambia por uno que solo él sepa. Mientras no lo cambie, el administrador conoce el PIN con el que ese supervisor autoriza — la pantalla de usuarios marca a quiénes les falta cambiarlo.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="90" r="11">
-      <c r="A11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Etiqueta — qué cabe</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>La etiqueta de ETIQUETAR mide 2.25 x 1.25 pulgadas (Dymo). A ese tamaño NO caben los 11 campos legibles con el código de barras encima. ¿Cuáles son los 4 o 5 imprescindibles, los que el operario tiene que leer de lejos en la estantería?</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Nuestra apuesta: (1) código de barras, (2) número de recepción, (3) código + nombre del cliente, (4) sucursal donde retira, (5) n/N de paquetes. Los 11 campos están listados en la hoja 3.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>El codigo del supervisor ya esta funcionando. ¿A quienes les asignamos PIN? Pueden tenerlo: Administrador, Supervisor Caja, Supervisor Pre-Factura y Supervisor de Servicio al Cliente.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Un administrador se los asigna desde la pantalla de usuarios y despues cada supervisor lo cambia por uno que solo el sepa. Mientras no lo cambie, el administrador conoce el PIN con el que ese supervisor autoriza — la pantalla de usuarios marca a quienes les falta cambiarlo.</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="16">
+      <c r="A16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Probar la etiqueta impresa</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Imprimi una etiqueta y decinos dos cosas: (1) si no se corta nada, sobre todo en un paquete que traiga tercero Y driver, que es el que mas campos lleva; (2) si el lector escanea bien el codigo de barras.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Los 11 campos van con la jerarquia de tamanos que marcaste. El codigo de barras quedo en 0.20 pulgadas de alto, que es el minimo practico para lectores de mano — es lo unico que no podemos probar nosotros. Los campos estan en la hoja 3.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="17">
+      <c r="A17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Proveedores de entrega personal</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>¿Confirmas esta lista para dejarla precargada? Entrega local / personal, Uber o delivery, Driver particular, Courier local.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Hoy no hay ninguno cargado, asi que la pantalla de Entrega Personal avisa que faltan configurar. En cualquier caso los podes crear, editar o desactivar vos mismo desde Catalogos → Proveedores.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -439,7 +439,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="4" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Preguntas para Yusef — 06 de Agosto de 2026</t>
+          <t>Preguntas para Yusef — 08 de Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -471,72 +471,49 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row customHeight="1" ht="78" r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>En la reunión del 8 de agosto ya contestaste tres: el cambio de servicio (L.100), la moneda de los cargos y el redondeo de libras. Esas ya no están acá.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="5"/>
+    <row customHeight="1" ht="78" r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Urgencia</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Pregunta</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Lo que sabemos hoy</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>TU RESPUESTA</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="78" r="6">
-      <c r="A6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Cambio de servicio</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>En tu hoja el cambio de servicio dice 5 y el titulo dice L100, con la nota "pasarlo a dolares". En el sistema esta cargado en $15. ¿Cual queda?</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Este cargo se genera SOLO, en una nota de debito, cada vez que se factura un paquete al que le cambiaron el servicio. Mientras no nos digas, sigue cobrando los $15 — que es el triple de los 5 de tu hoja.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="78" r="7">
       <c r="A7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
@@ -545,17 +522,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Moneda de 10 cargos</t>
+          <t>Formato del N° de recepcion</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Necesitamos la moneda de 10 cargos de tu hoja. Estan en la HOJA 4 con la duda de cada uno y una columna para que escribas $ o LPS.</t>
+          <t>Dijiste que al numero de recepcion le falta el MES, y que ya nos lo habias mandado. ¿Nos pasas el formato exacto? Ejemplo de como quedaria un paquete recibido en Miami en agosto 2026.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>En tu hoja pusiste la leyenda "precios en $" y "precios en lempiras" pero las celdas de precio quedaron sin colorear, asi que un 5 no dice si son 5 dolares o 5 lempiras. Ya cargamos los 5 que si dejaste claros con una nota escrita.</t>
+          <t>Hoy el numero es RM + anio + correlativo de 6 digitos: RM0002026000010. El correlativo reinicia cada enero. Cambiar el formato toca todos los numeros ya generados, por eso no lo inventamos nosotros.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -566,7 +543,7 @@
     </row>
     <row customHeight="1" ht="78" r="8">
       <c r="A8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -575,17 +552,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Recolecta: ¿zona o plano?</t>
+          <t>Redondeo de libras</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Vos pediste que la recolecta se cobrara POR ZONA en vez de $35 fijos, y asi esta hecho. Pero tu hoja nueva dice 35 plano. ¿Cual mandamos?</t>
+          <t>La regla que diste (1.09 se cobra 1.0, 1.10 se cobra 1.5, 1.60 se cobra 2.0) es para escalones de MEDIA libra. Si armas una tarifa con escalon de 1 libra entera, ¿la tolerancia sigue siendo 0.09?</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Hoy el sistema tiene una tabla de tarifas de recolecta por zona/distancia, que es lo que pediste en su momento. Si mandamos el 35 plano, esa tabla deja de usarse.</t>
+          <t>Hoy el sistema no redondea: cobra el peso exacto. Cuando actives el escalonado va a redondear, y necesitamos la regla completa para no cobrarte de mas a vos ni de menos al cliente.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -596,26 +573,26 @@
     </row>
     <row customHeight="1" ht="78" r="9">
       <c r="A9" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Revisar los precios cargados</t>
+          <t>Recolecta: ¿zona o plano?</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>En la HOJA 2 esta TODO lo que quedo cargado de tu tabla, leido directo del sistema. Es literalmente lo que va a cobrar. ¿Esta bien?</t>
+          <t>Vos pediste que la recolecta se cobrara POR ZONA en vez de $35 fijos, y asi esta hecho. En el audio dijiste "$35 normal, pero hay clientes con descuento". ¿La recolecta de MIAMI y la de HONDURAS son dos cosas distintas?</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". Si algo esta mal, escribilo en la ultima columna de esa hoja.</t>
+          <t>Hoy el sistema tiene una tabla de tarifas de recolecta por zona/distancia, que es lo que pediste en su momento. Si el $35 de Miami es otro cargo aparte, conviven los dos sin problema.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -626,26 +603,26 @@
     </row>
     <row customHeight="1" ht="78" r="10">
       <c r="A10" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Las categorías no bajan de escalón</t>
+          <t>Manejo y gastos de destino</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Un cliente "Clientes Amigos" con 200 libras de CER paga $4.20 la libra ($840) mientras el publico paga $3.50 ($700). ¿Es asi, o las categorias tambien deberian bajar de escalon?</t>
+          <t>Tu hoja dice textual "ponerlo lps1 mas isv", pero en el audio dijiste que es "parecido al de ajuste", y ajuste es en dolares. ¿Lempiras o dolares?</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Tu tabla da un solo precio por categoria (columna NORMAL) y los tarifarios escalonados los declaraste solo para el Precio Normal. Lo cargamos literal a como lo mandaste, pero el resultado es que un amigo paga mas que un cliente de mostrador en paquetes grandes.</t>
+          <t>Lo dejamos en Lempiras, que es lo que dice la nota escrita de tu hoja. Es el unico cargo donde el audio y la hoja no coinciden.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -656,7 +633,7 @@
     </row>
     <row customHeight="1" ht="78" r="11">
       <c r="A11" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -665,17 +642,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>CKM cae en dos reglas</t>
+          <t>Retornado de Miami</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Para CKM, ¿cual minimo manda: los L.200, el de libras, o el que resulte MAYOR de los dos?</t>
+          <t>Dijiste "$5 es como un precio minimo" y que si va por USPS sube a $15 porque hay que pagar motorista. ¿Son dos cargos distintos, o uno con minimo de $5?</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>En el audio dijiste "los servicios serie CK son 200 lempiras ya con ISV" (aplica a CKA y CKM) y tambien "el maritimo lo tenemos estipulado en cantidad de libras" (aplica a CEM y CKM). CKM es las dos cosas. En tu tabla le pusiste L.173.91, asi que cargamos ese.</t>
+          <t>Cargado a $5. Si son dos, los damos de alta por separado y en Miami eligen cual aplica.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -686,7 +663,7 @@
     </row>
     <row customHeight="1" ht="78" r="12">
       <c r="A12" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
@@ -695,17 +672,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Mínimo en libras de CEM y CKM</t>
+          <t>Entrada y salida (IN &amp; OUT)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>¿Hace falta todavia un minimo en LIBRAS para CEM y CKM, o con el minimo en dinero de tu tabla ya esta?</t>
+          <t>Dijiste que es "de 10 a 5 depende". ¿De que depende — del tamano del paquete, del cliente, de la cantidad?</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Tu tabla trae el minimo en dinero (L.200 con ISV) pero no el de libras. En la practica el escalonado ya cubre el paquete chico: un CEM de 2 libras paga $4.50 la libra. Documentado en abril: CEM = 8 libras, CKM = 20 libras. En el audio dijiste 3 o 4 libras.</t>
+          <t>Es cuando el cliente recibe en Miami y lo recoge el mismo. Nos diste el ejemplo de 3 paquetes a $5 cada uno.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -716,7 +693,7 @@
     </row>
     <row customHeight="1" ht="78" r="13">
       <c r="A13" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -725,17 +702,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Regular y VIP</t>
+          <t>Flete Mexico y etiqueta internacional</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hay 8 clientes en las categorias "Regular" y "VIP", que no aparecen en tu tabla. ¿A cual de las nuevas los pasamos, o los dejamos como estan?</t>
+          <t>Dos cosas: (a) el flete de Mexico a Honduras, ¿en que moneda? (b) la creacion de etiqueta internacional que mencionaste, ¿que precio y en que moneda?</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Por ahora se quedaron con los precios viejos, que son mas bajos que los de lista. Las categorias de tu tabla son: Clientes Amigos, doTERRA/Farmasi, Familia, Mayoristas, Personal de CEC, Shein, Revendedores y Sin Cobro Minimo.</t>
+          <t>El flete Mexico esta en tu hoja con precio pero sin moneda. La etiqueta internacional no esta ni en la hoja ni en el sistema — la mencionaste como parte de los retornados de Miami.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -746,7 +723,7 @@
     </row>
     <row customHeight="1" ht="78" r="14">
       <c r="A14" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
@@ -755,17 +732,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mayoristas incompleto</t>
+          <t>Buscar cliente por los ultimos digitos</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>De MAYORISTAS solo vino el precio de CKM ($1.50). Los otros cuatro servicios vinieron en cero. ¿Que cobran los mayoristas en CER, CKA, EXPRESS y CEM?</t>
+          <t>Pediste que se pueda escribir solo el final del codigo (2867, o hasta un solo 6) y que caiga. Con codigos de 5 digitos, escribir un 6 va a traer cientos. ¿Mostramos todos los que terminan en 6, o priorizamos el que coincide exacto?</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Mientras tanto esos cuatro siguen con los valores viejos del sistema, que no salieron de tu tabla. FAMILIA y REVENDEDORES vinieron todos en cero, asi que sus clientes pagan precio de lista.</t>
+          <t>Asi trabajan hoy en el sistema viejo, y los codigos viejos de 4 digitos no se van a migrar.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -776,7 +753,7 @@
     </row>
     <row customHeight="1" ht="78" r="15">
       <c r="A15" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -785,17 +762,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>PINs de los supervisores</t>
+          <t>Guardar: ¿F8 o F10?</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>El codigo del supervisor ya esta funcionando. ¿A quienes les asignamos PIN? Pueden tenerlo: Administrador, Supervisor Caja, Supervisor Pre-Factura y Supervisor de Servicio al Cliente.</t>
+          <t>En etiquetar guardar es F8, pero en pre-facturas, ventas, caja y financiamientos es F10 — y vos apretaste F10 sin pensarlo. ¿Lo pasamos todo a F10?</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Un administrador se los asigna desde la pantalla de usuarios y despues cada supervisor lo cambia por uno que solo el sepa. Mientras no lo cambie, el administrador conoce el PIN con el que ese supervisor autoriza — la pantalla de usuarios marca a quienes les falta cambiarlo.</t>
+          <t>F8 en el resto del sistema es "exportar a Excel". Si cambiamos, hay que avisarle a Miami que ya tiene el F8 en el dedo.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -806,7 +783,7 @@
     </row>
     <row customHeight="1" ht="78" r="16">
       <c r="A16" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
@@ -815,17 +792,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Probar la etiqueta impresa</t>
+          <t>Peso por caja</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Imprimi una etiqueta y decinos dos cosas: (1) si no se corta nada, sobre todo en un paquete que traiga tercero Y driver, que es el que mas campos lleva; (2) si el lector escanea bien el codigo de barras.</t>
+          <t>Si son 2 cajas, ¿preferis que salgan las 2 lineas de peso y medidas de una vez, o un boton "agregar" que las va sumando de a una?</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Los 11 campos van con la jerarquia de tamanos que marcaste. El codigo de barras quedo en 0.20 pulgadas de alto, que es el minimo practico para lectores de mano — es lo unico que no podemos probar nosotros. Los campos estan en la hoja 3.</t>
+          <t>Hoy pide una sola linea aunque sean varias cajas. Vos mencionaste las dos formas y dejaste elegir.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -836,29 +813,389 @@
     </row>
     <row customHeight="1" ht="78" r="17">
       <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Bajar la cantidad de cajas</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Si un paquete tiene 5 cajas y alguien lo baja a 2, las otras 3 se borran. ¿Que hacemos si alguna de esas ya esta facturada o entregada?</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Hoy no se borra ninguna y quedan registros de mas, que es el error que viste. Lo mas seguro es no dejar borrar una caja ya facturada y avisar por que.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="18">
+      <c r="A18" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Origen del paquete</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>El campo de origen (Estados Unidos / China) esta en pantalla sin definir. ¿Que origenes van, y cambia algo del cobro segun el origen?</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Dijiste "como ahorita estamos en Estados Unidos, pero ya va a abrir China".</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="19">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Listas que quedaste de mandar</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Nos faltan tres listas tuyas: (a) motivos de retencion completos — sabemos que falta "solicitado por el cliente para retorno"; (b) las notas predeterminadas de pre-factura, caja y servicio al cliente; (c) las grabaciones de voz para la alerta de pre-alerta.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Los motivos y las notas van a quedar editables por vos, asi que podes agregarlos vos mismo despues. Las grabaciones son las que hizo tu senora en 2022 — dijiste que las volvias a grabar.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="20">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Sonidos de etiquetar</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Te vamos a pasar una lista de sonidos para que elijas el de ERROR (el "feo", para cuando el paquete no es del tipo de envio de la sesion). ¿Preferis elegir vos o te proponemos uno?</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>El pin agradable que ya suena lo aprobaste. Faltan: el pito de "este tracking ya existia", el de error, y el pin antes de que salga cada modal.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="21">
+      <c r="A21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Revisar los precios cargados</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>En la HOJA 2 esta TODO lo que quedo cargado de tu tabla, leido directo del sistema. Es literalmente lo que va a cobrar. ¿Esta bien?</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Tomamos la hoja PROPUESTA de "precios por categoria 2026.xlsx". Si algo esta mal, escribilo en la ultima columna de esa hoja.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="22">
+      <c r="A22" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Las categorías no bajan de escalón</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Un cliente "Clientes Amigos" con 200 libras de CER paga $4.20 la libra ($840) mientras el publico paga $3.50 ($700). ¿Es asi, o las categorias tambien deberian bajar de escalon?</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Tu tabla da un solo precio por categoria (columna NORMAL) y los tarifarios escalonados los declaraste solo para el Precio Normal. Lo cargamos literal a como lo mandaste, pero el resultado es que un amigo paga mas que un cliente de mostrador en paquetes grandes.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="23">
+      <c r="A23" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>CKM cae en dos reglas</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Para CKM, ¿cual minimo manda: los L.200, el de libras, o el que resulte MAYOR de los dos?</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>En el audio dijiste "los servicios serie CK son 200 lempiras ya con ISV" (aplica a CKA y CKM) y tambien "el maritimo lo tenemos estipulado en cantidad de libras" (aplica a CEM y CKM). CKM es las dos cosas. En tu tabla le pusiste L.173.91, asi que cargamos ese.</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="24">
+      <c r="A24" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Mínimo en libras de CEM y CKM</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>¿Hace falta todavia un minimo en LIBRAS para CEM y CKM, o con el minimo en dinero de tu tabla ya esta?</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Tu tabla trae el minimo en dinero (L.200 con ISV) pero no el de libras. En la practica el escalonado ya cubre el paquete chico: un CEM de 2 libras paga $4.50 la libra. Documentado en abril: CEM = 8 libras, CKM = 20 libras. En el audio dijiste 3 o 4 libras.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="25">
+      <c r="A25" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Regular y VIP</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Hay 8 clientes en las categorias "Regular" y "VIP", que no aparecen en tu tabla. ¿A cual de las nuevas los pasamos, o los dejamos como estan?</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Por ahora se quedaron con los precios viejos, que son mas bajos que los de lista. Las categorias de tu tabla son: Clientes Amigos, doTERRA/Farmasi, Familia, Mayoristas, Personal de CEC, Shein, Revendedores y Sin Cobro Minimo.</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="26">
+      <c r="A26" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Mayoristas incompleto</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>De MAYORISTAS solo vino el precio de CKM ($1.50). Los otros cuatro servicios vinieron en cero. ¿Que cobran los mayoristas en CER, CKA, EXPRESS y CEM?</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Mientras tanto esos cuatro siguen con los valores viejos del sistema, que no salieron de tu tabla. FAMILIA y REVENDEDORES vinieron todos en cero, asi que sus clientes pagan precio de lista.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="27">
+      <c r="A27" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>PINs de los supervisores</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>El codigo del supervisor ya esta funcionando. ¿A quienes les asignamos PIN? Pueden tenerlo: Administrador, Supervisor Caja, Supervisor Pre-Factura y Supervisor de Servicio al Cliente.</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Un administrador se los asigna desde la pantalla de usuarios y despues cada supervisor lo cambia por uno que solo el sepa. Mientras no lo cambie, el administrador conoce el PIN con el que ese supervisor autoriza — la pantalla de usuarios marca a quienes les falta cambiarlo.</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="28">
+      <c r="A28" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Probar la etiqueta impresa</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Imprimi una etiqueta y decinos dos cosas: (1) si no se corta nada, sobre todo en un paquete que traiga tercero Y driver, que es el que mas campos lleva; (2) si el lector escanea bien el codigo de barras.</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Los 11 campos van con la jerarquia de tamanos que marcaste. El codigo de barras quedo en 0.20 pulgadas de alto, que es el minimo practico para lectores de mano — es lo unico que no podemos probar nosotros. Los campos estan en la hoja 3.</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="78" r="29">
+      <c r="A29" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>BAJA</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Proveedores de entrega personal</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>¿Confirmas esta lista para dejarla precargada? Entrega local / personal, Uber o delivery, Driver particular, Courier local.</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Hoy no hay ninguno cargado, asi que la pantalla de Entrega Personal avisa que faltan configurar. En cualquier caso los podes crear, editar o desactivar vos mismo desde Catalogos → Proveedores.</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/docs/entregables/preguntas_para_yusef.xlsx
+++ b/docs/entregables/preguntas_para_yusef.xlsx
@@ -453,7 +453,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Preguntas para Yusef — 08 de Agosto de 2026</t>
+          <t>Preguntas para Yusef — 10 de Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Clientes Amigos</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>$2.20</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>doTERRA / Farmasi</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>$1.70</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Mayorista</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$1.75</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Personal CEC</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>$1.80</t>
+          <t>$1.90</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>$2.07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>$1.80</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$2.20</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>$1.75</t>
+          <t>$1.70</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Humuya TGU</t>
+          <t>todas</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>$1.90</t>
+          <t>$1.80</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2.07</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1.80</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Sin Cobro Mínimo</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$1.50</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Clientes Amigos</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>$4.20</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>$5.75</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>doTERRA / Farmasi</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2322,22 +2322,22 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$4.50</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>$5.75</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Mayorista</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Personal CEC</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$4.20</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.75</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.75</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sin Cobro Mínimo</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>$4.50</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Clientes Amigos</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>$3.80</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>$5.75</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>doTERRA / Farmasi</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>$5.75</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Mayorista</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$3.00</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.45</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.00</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Personal CEC</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>$3.45</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2983,17 +2983,17 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$3.80</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.75</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.75</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sin Cobro Mínimo</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>$4.00</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Humuya TGU</t>
+          <t>todas</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Clientes Amigos</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>$1.70</t>
+          <t>$1.50</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>doTERRA / Farmasi</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>$1.70</t>
+          <t>$1.90</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Mayorista</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$1.90</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Personal CEC</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>$1.70</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>$1.61</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$1.70</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>$1.75</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1.61</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Humuya TGU</t>
+          <t>todas</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>$1.90</t>
+          <t>$1.75</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Sin Cobro Mínimo</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>$1.90</t>
+          <t>$1.50</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Clientes Amigos</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>$7.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>$11.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>doTERRA / Farmasi</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>$7.00</t>
+          <t>$7.50</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>$11.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Mayorista</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$6.50</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Personal CEC</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>$6.50</t>
+          <t>$7.00</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -4295,17 +4295,17 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$7.00</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.50</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>⚠ No venía en tu tabla — quedó del arranque</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>Precio de lista (público)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.50</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Sin Cobro Mínimo</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t/>
+          <t>⚠ No venía en tu tabla — quedó del arranque</t>
         </is>
       </c>
     </row>
